--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H617"/>
+  <dimension ref="A1:H620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18906,7 +18906,7 @@
         <v>313.68</v>
       </c>
       <c r="D616" t="n">
-        <v>321.37</v>
+        <v>321.71</v>
       </c>
       <c r="E616" t="n">
         <v>321.87</v>
@@ -18936,7 +18936,7 @@
         <v>312.6</v>
       </c>
       <c r="D617" t="n">
-        <v>321.48</v>
+        <v>321.86</v>
       </c>
       <c r="E617" t="n">
         <v>321.38</v>
@@ -18948,6 +18948,96 @@
         <v>318.56</v>
       </c>
       <c r="H617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="C618" t="n">
+        <v>312.76</v>
+      </c>
+      <c r="D618" t="n">
+        <v>322.42</v>
+      </c>
+      <c r="E618" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="F618" t="n">
+        <v>315.34</v>
+      </c>
+      <c r="G618" t="n">
+        <v>319.81</v>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>320.15</v>
+      </c>
+      <c r="C619" t="n">
+        <v>313.01</v>
+      </c>
+      <c r="D619" t="n">
+        <v>322.18</v>
+      </c>
+      <c r="E619" t="n">
+        <v>321.48</v>
+      </c>
+      <c r="F619" t="n">
+        <v>316.08</v>
+      </c>
+      <c r="G619" t="n">
+        <v>320.98</v>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>320.82</v>
+      </c>
+      <c r="C620" t="n">
+        <v>313.36</v>
+      </c>
+      <c r="D620" t="n">
+        <v>322.32</v>
+      </c>
+      <c r="E620" t="n">
+        <v>321.26</v>
+      </c>
+      <c r="F620" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="G620" t="n">
+        <v>320.71</v>
+      </c>
+      <c r="H620" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18964,7 +19054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26187,6 +26277,56 @@
       </c>
       <c r="B722" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -26355,28 +26495,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02904990954484281</v>
+        <v>-0.03098901520871791</v>
       </c>
       <c r="J2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002089233231378107</v>
+        <v>0.002397191142819</v>
       </c>
       <c r="M2" t="n">
-        <v>3.53385200051799</v>
+        <v>3.526612296357969</v>
       </c>
       <c r="N2" t="n">
-        <v>17.97468389848711</v>
+        <v>17.90578712956103</v>
       </c>
       <c r="O2" t="n">
-        <v>4.239656106158507</v>
+        <v>4.231523027180761</v>
       </c>
       <c r="P2" t="n">
-        <v>322.9687912307891</v>
+        <v>322.9923533223295</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26437,28 +26577,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3398793734913026</v>
+        <v>-0.3412499493172214</v>
       </c>
       <c r="J3" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K3" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L3" t="n">
-        <v>0.451857810742409</v>
+        <v>0.4558701007900486</v>
       </c>
       <c r="M3" t="n">
-        <v>1.931553057272058</v>
+        <v>1.928467909042151</v>
       </c>
       <c r="N3" t="n">
-        <v>6.248963151852267</v>
+        <v>6.227726627796645</v>
       </c>
       <c r="O3" t="n">
-        <v>2.499792621769307</v>
+        <v>2.495541349646734</v>
       </c>
       <c r="P3" t="n">
-        <v>323.3340403622371</v>
+        <v>323.3506943611899</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26519,28 +26659,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1642151556162233</v>
+        <v>-0.1625119274005184</v>
       </c>
       <c r="J4" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K4" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1811033084449455</v>
+        <v>0.1791239589769386</v>
       </c>
       <c r="M4" t="n">
-        <v>1.793471776684866</v>
+        <v>1.792101178000168</v>
       </c>
       <c r="N4" t="n">
-        <v>5.437460489414824</v>
+        <v>5.422720879517684</v>
       </c>
       <c r="O4" t="n">
-        <v>2.331836291298088</v>
+        <v>2.328673630957693</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1881468924997</v>
+        <v>325.1674565125864</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -26601,28 +26741,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2503405707185222</v>
+        <v>-0.2526288984198251</v>
       </c>
       <c r="J5" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K5" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3273443345995383</v>
+        <v>0.332541992334573</v>
       </c>
       <c r="M5" t="n">
-        <v>1.82992188582047</v>
+        <v>1.830143090273329</v>
       </c>
       <c r="N5" t="n">
-        <v>5.742716286997839</v>
+        <v>5.739398475606468</v>
       </c>
       <c r="O5" t="n">
-        <v>2.396396521237218</v>
+        <v>2.395704171137678</v>
       </c>
       <c r="P5" t="n">
-        <v>330.3360685737432</v>
+        <v>330.3638799407954</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -26683,28 +26823,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2570602900941444</v>
+        <v>-0.2581308435019984</v>
       </c>
       <c r="J6" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K6" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2990994638802632</v>
+        <v>0.302688744505331</v>
       </c>
       <c r="M6" t="n">
-        <v>2.107350984652411</v>
+        <v>2.101656771273129</v>
       </c>
       <c r="N6" t="n">
-        <v>6.905222130474279</v>
+        <v>6.877539168601566</v>
       </c>
       <c r="O6" t="n">
-        <v>2.627778934856256</v>
+        <v>2.622506276179633</v>
       </c>
       <c r="P6" t="n">
-        <v>323.5037413371447</v>
+        <v>323.5167504058761</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -26765,28 +26905,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1452944465138068</v>
+        <v>-0.1475006842052672</v>
       </c>
       <c r="J7" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K7" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06870411879498217</v>
+        <v>0.07116614605912541</v>
       </c>
       <c r="M7" t="n">
-        <v>2.870154826275346</v>
+        <v>2.866989914701858</v>
       </c>
       <c r="N7" t="n">
-        <v>12.76056334717335</v>
+        <v>12.72258983619816</v>
       </c>
       <c r="O7" t="n">
-        <v>3.572193072493892</v>
+        <v>3.566873958552245</v>
       </c>
       <c r="P7" t="n">
-        <v>326.499425490738</v>
+        <v>326.5262339990399</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -26828,7 +26968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H617"/>
+  <dimension ref="A1:H620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52679,7 +52819,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>-45.16747412318603,170.90917069556772</t>
+          <t>-45.16747615980248,170.90917392317692</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -52721,7 +52861,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>-45.16747478209137,170.9091717397942</t>
+          <t>-45.16747705830971,170.90917534712224</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -52740,6 +52880,132 @@
         </is>
       </c>
       <c r="H617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-45.16654255861429,170.91041301609144</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-45.16692395321701,170.90966439411918</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>-45.16748041273654,170.90918066318517</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-45.16795174256152,170.90855916040198</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-45.16846229655668,170.90800832298135</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-45.168986120620104,170.9075293511883</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-45.16654427053305,170.91041507935054</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-45.16692553823064,170.9096666509261</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>-45.16747897512506,170.9091783848724</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-45.16795029455601,170.9085565625058</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-45.16846614059089,170.90801600965926</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-45.1689925247366,170.9075411648609</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-45.166548858475124,170.91042060888552</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-45.16692775724965,170.90966981045605</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>-45.16747981373175,170.90917971388816</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-45.16794906932053,170.9085543642861</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-45.16846380300259,170.90801133532796</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-45.16899104686367,170.90753843862854</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -19054,7 +19054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26327,6 +26327,26 @@
       </c>
       <c r="B727" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H620"/>
+  <dimension ref="A1:H621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19040,6 +19040,36 @@
       <c r="H620" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>322.31</v>
+      </c>
+      <c r="C621" t="n">
+        <v>312.89</v>
+      </c>
+      <c r="D621" t="n">
+        <v>322.99</v>
+      </c>
+      <c r="E621" t="n">
+        <v>321.07</v>
+      </c>
+      <c r="F621" t="n">
+        <v>315.85</v>
+      </c>
+      <c r="G621" t="n">
+        <v>320.18</v>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B729"/>
+  <dimension ref="A1:B730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26347,6 +26377,16 @@
       </c>
       <c r="B729" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -26515,28 +26555,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03098901520871791</v>
+        <v>-0.03094260953885515</v>
       </c>
       <c r="J2" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K2" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002397191142819</v>
+        <v>0.002397812617602857</v>
       </c>
       <c r="M2" t="n">
-        <v>3.526612296357969</v>
+        <v>3.521127571543331</v>
       </c>
       <c r="N2" t="n">
-        <v>17.90578712956103</v>
+        <v>17.87693643680439</v>
       </c>
       <c r="O2" t="n">
-        <v>4.231523027180761</v>
+        <v>4.228112632937347</v>
       </c>
       <c r="P2" t="n">
-        <v>322.9923533223295</v>
+        <v>322.9917858551422</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26597,28 +26637,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3412499493172214</v>
+        <v>-0.3417396797527818</v>
       </c>
       <c r="J3" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K3" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4558701007900486</v>
+        <v>0.4572587055500243</v>
       </c>
       <c r="M3" t="n">
-        <v>1.928467909042151</v>
+        <v>1.927558708930364</v>
       </c>
       <c r="N3" t="n">
-        <v>6.227726627796645</v>
+        <v>6.220979498474237</v>
       </c>
       <c r="O3" t="n">
-        <v>2.495541349646734</v>
+        <v>2.494189146491147</v>
       </c>
       <c r="P3" t="n">
-        <v>323.3506943611899</v>
+        <v>323.3566829818395</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26679,28 +26719,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1625119274005184</v>
+        <v>-0.1617874550748728</v>
       </c>
       <c r="J4" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K4" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1791239589769386</v>
+        <v>0.1780956540525894</v>
       </c>
       <c r="M4" t="n">
-        <v>1.792101178000168</v>
+        <v>1.792313161256112</v>
       </c>
       <c r="N4" t="n">
-        <v>5.422720879517684</v>
+        <v>5.421191048696052</v>
       </c>
       <c r="O4" t="n">
-        <v>2.328673630957693</v>
+        <v>2.328345130923689</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1674565125864</v>
+        <v>325.1585973737329</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -26761,28 +26801,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2526288984198251</v>
+        <v>-0.2535215103243024</v>
       </c>
       <c r="J5" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K5" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L5" t="n">
-        <v>0.332541992334573</v>
+        <v>0.3344096926798209</v>
       </c>
       <c r="M5" t="n">
-        <v>1.830143090273329</v>
+        <v>1.830686737439143</v>
       </c>
       <c r="N5" t="n">
-        <v>5.739398475606468</v>
+        <v>5.741096269594181</v>
       </c>
       <c r="O5" t="n">
-        <v>2.395704171137678</v>
+        <v>2.396058486263259</v>
       </c>
       <c r="P5" t="n">
-        <v>330.3638799407954</v>
+        <v>330.374795158015</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -26843,28 +26883,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2581308435019984</v>
+        <v>-0.2584154574167087</v>
       </c>
       <c r="J6" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K6" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L6" t="n">
-        <v>0.302688744505331</v>
+        <v>0.3038086809386339</v>
       </c>
       <c r="M6" t="n">
-        <v>2.101656771273129</v>
+        <v>2.099446157680346</v>
       </c>
       <c r="N6" t="n">
-        <v>6.877539168601566</v>
+        <v>6.867560131815106</v>
       </c>
       <c r="O6" t="n">
-        <v>2.622506276179633</v>
+        <v>2.620603009197522</v>
       </c>
       <c r="P6" t="n">
-        <v>323.5167504058761</v>
+        <v>323.5202307792469</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -26925,28 +26965,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1475006842052672</v>
+        <v>-0.1483372908906478</v>
       </c>
       <c r="J7" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K7" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07116614605912541</v>
+        <v>0.07208463933966047</v>
       </c>
       <c r="M7" t="n">
-        <v>2.866989914701858</v>
+        <v>2.866366757208565</v>
       </c>
       <c r="N7" t="n">
-        <v>12.72258983619816</v>
+        <v>12.71169285751539</v>
       </c>
       <c r="O7" t="n">
-        <v>3.566873958552245</v>
+        <v>3.565346106272909</v>
       </c>
       <c r="P7" t="n">
-        <v>326.5262339990399</v>
+        <v>326.536464361925</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -26988,7 +27028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H620"/>
+  <dimension ref="A1:H621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53031,6 +53071,48 @@
         </is>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-45.166559061509574,170.9104329059143</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-45.16692477742409,170.90966556765875</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-45.16748382706359,170.9091860741784</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-45.16794801116259,170.90855246582367</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-45.16846494582356,170.90801362055655</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-45.168988145853646,170.90753308713573</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H621"/>
+  <dimension ref="A1:H625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19070,6 +19070,126 @@
       <c r="H621" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>323.04</v>
+      </c>
+      <c r="C622" t="n">
+        <v>312.02</v>
+      </c>
+      <c r="D622" t="n">
+        <v>322.46</v>
+      </c>
+      <c r="E622" t="n">
+        <v>320.11</v>
+      </c>
+      <c r="F622" t="n">
+        <v>314.57</v>
+      </c>
+      <c r="G622" t="n">
+        <v>320.02</v>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>323.1</v>
+      </c>
+      <c r="C623" t="n">
+        <v>312.73</v>
+      </c>
+      <c r="D623" t="n">
+        <v>322.53</v>
+      </c>
+      <c r="E623" t="n">
+        <v>320.22</v>
+      </c>
+      <c r="F623" t="n">
+        <v>313.62</v>
+      </c>
+      <c r="G623" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="C624" t="n">
+        <v>310.96</v>
+      </c>
+      <c r="D624" t="n">
+        <v>321.75</v>
+      </c>
+      <c r="E624" t="n">
+        <v>318.96</v>
+      </c>
+      <c r="F624" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="G624" t="n">
+        <v>319.63</v>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>323.29</v>
+      </c>
+      <c r="C625" t="n">
+        <v>311.56</v>
+      </c>
+      <c r="D625" t="n">
+        <v>321.77</v>
+      </c>
+      <c r="E625" t="n">
+        <v>319.4</v>
+      </c>
+      <c r="F625" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="G625" t="n">
+        <v>320.49</v>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B730"/>
+  <dimension ref="A1:B734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26387,6 +26507,46 @@
       </c>
       <c r="B730" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -26555,28 +26715,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03094260953885515</v>
+        <v>-0.0297589488358728</v>
       </c>
       <c r="J2" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K2" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002397812617602857</v>
+        <v>0.002246675544383625</v>
       </c>
       <c r="M2" t="n">
-        <v>3.521127571543331</v>
+        <v>3.503664402105679</v>
       </c>
       <c r="N2" t="n">
-        <v>17.87693643680439</v>
+        <v>17.76740575629621</v>
       </c>
       <c r="O2" t="n">
-        <v>4.228112632937347</v>
+        <v>4.215140063662917</v>
       </c>
       <c r="P2" t="n">
-        <v>322.9917858551422</v>
+        <v>322.9772654911348</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26637,28 +26797,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3417396797527818</v>
+        <v>-0.3450785885445136</v>
       </c>
       <c r="J3" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K3" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4572587055500243</v>
+        <v>0.4636863136462501</v>
       </c>
       <c r="M3" t="n">
-        <v>1.927558708930364</v>
+        <v>1.930281492061516</v>
       </c>
       <c r="N3" t="n">
-        <v>6.220979498474237</v>
+        <v>6.222095178930202</v>
       </c>
       <c r="O3" t="n">
-        <v>2.494189146491147</v>
+        <v>2.494412792408306</v>
       </c>
       <c r="P3" t="n">
-        <v>323.3566829818395</v>
+        <v>323.3976464259224</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26719,28 +26879,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1617874550748728</v>
+        <v>-0.1600829455557642</v>
       </c>
       <c r="J4" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K4" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1780956540525894</v>
+        <v>0.1766130638886977</v>
       </c>
       <c r="M4" t="n">
-        <v>1.792313161256112</v>
+        <v>1.788076610283721</v>
       </c>
       <c r="N4" t="n">
-        <v>5.421191048696052</v>
+        <v>5.397309249048287</v>
       </c>
       <c r="O4" t="n">
-        <v>2.328345130923689</v>
+        <v>2.323210978161107</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1585973737329</v>
+        <v>325.1376936158095</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -26801,28 +26961,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2535215103243024</v>
+        <v>-0.2588930405273516</v>
       </c>
       <c r="J5" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K5" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3344096926798209</v>
+        <v>0.3427904694890338</v>
       </c>
       <c r="M5" t="n">
-        <v>1.830686737439143</v>
+        <v>1.840203535778033</v>
       </c>
       <c r="N5" t="n">
-        <v>5.741096269594181</v>
+        <v>5.805262836201299</v>
       </c>
       <c r="O5" t="n">
-        <v>2.396058486263259</v>
+        <v>2.409411304904436</v>
       </c>
       <c r="P5" t="n">
-        <v>330.374795158015</v>
+        <v>330.4406930286445</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -26883,28 +27043,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2584154574167087</v>
+        <v>-0.2631049753342712</v>
       </c>
       <c r="J6" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K6" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3038086809386339</v>
+        <v>0.3117060713227371</v>
       </c>
       <c r="M6" t="n">
-        <v>2.099446157680346</v>
+        <v>2.105241059304822</v>
       </c>
       <c r="N6" t="n">
-        <v>6.867560131815106</v>
+        <v>6.905463279213602</v>
       </c>
       <c r="O6" t="n">
-        <v>2.620603009197522</v>
+        <v>2.627824818973594</v>
       </c>
       <c r="P6" t="n">
-        <v>323.5202307792469</v>
+        <v>323.5777727066542</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -26965,28 +27125,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1483372908906478</v>
+        <v>-0.1517097994994237</v>
       </c>
       <c r="J7" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K7" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07208463933966047</v>
+        <v>0.07584071184155428</v>
       </c>
       <c r="M7" t="n">
-        <v>2.866366757208565</v>
+        <v>2.864019399992311</v>
       </c>
       <c r="N7" t="n">
-        <v>12.71169285751539</v>
+        <v>12.67003230753629</v>
       </c>
       <c r="O7" t="n">
-        <v>3.565346106272909</v>
+        <v>3.559498884328564</v>
       </c>
       <c r="P7" t="n">
-        <v>326.536464361925</v>
+        <v>326.5778329941924</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27028,7 +27188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H621"/>
+  <dimension ref="A1:H625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53113,6 +53273,174 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-45.16656406031124,170.91043893063468</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-45.16691926157641,170.9096577139713</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-45.16748065233845,170.90918104290395</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-45.167942664679885,170.90854287359363</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-45.16845829668273,170.9080003246825</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-45.168987270077,170.90753147159086</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-45.16656447117163,170.91043942581723</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-45.166923763015376,170.90966412330235</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-45.167481071641774,170.90918170741188</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-45.16794327729773,170.90854397270323</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-45.168453361772556,170.90799045665298</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-45.16898863847801,170.90753399587976</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-45.16656207448596,170.91043653725248</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-45.166912541117604,170.9096481451128</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-45.1674763994044,170.9091743028957</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-45.16793626003812,170.90853138290376</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-45.16844858270086,170.90798090024705</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-45.16898513537131,170.90752753370043</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-45.166565772229546,170.91044099389532</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-45.16691634515098,170.90965356144756</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-45.16747651920537,170.90917449275506</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-45.16793871050989,170.90853577934132</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-45.16844442698572,170.90797259033022</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-45.16898984267087,170.90753621725412</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19188,6 +19188,126 @@
         <v>320.49</v>
       </c>
       <c r="H625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="C626" t="n">
+        <v>312.59</v>
+      </c>
+      <c r="D626" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="E626" t="n">
+        <v>319.78</v>
+      </c>
+      <c r="F626" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="G626" t="n">
+        <v>320.28</v>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="C627" t="n">
+        <v>312.59</v>
+      </c>
+      <c r="D627" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="E627" t="n">
+        <v>319.78</v>
+      </c>
+      <c r="F627" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="G627" t="n">
+        <v>317.57</v>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>323.42</v>
+      </c>
+      <c r="C628" t="n">
+        <v>311.85</v>
+      </c>
+      <c r="D628" t="n">
+        <v>321.94</v>
+      </c>
+      <c r="E628" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="F628" t="n">
+        <v>311.41</v>
+      </c>
+      <c r="G628" t="n">
+        <v>317.82</v>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="C629" t="n">
+        <v>312.79</v>
+      </c>
+      <c r="D629" t="n">
+        <v>320.65</v>
+      </c>
+      <c r="E629" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="F629" t="n">
+        <v>310.2</v>
+      </c>
+      <c r="G629" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="H629" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19204,7 +19324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B734"/>
+  <dimension ref="A1:B738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26547,6 +26667,46 @@
       </c>
       <c r="B734" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -26715,28 +26875,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0297589488358728</v>
+        <v>-0.02829787087390958</v>
       </c>
       <c r="J2" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="K2" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002246675544383625</v>
+        <v>0.002057049467040772</v>
       </c>
       <c r="M2" t="n">
-        <v>3.503664402105679</v>
+        <v>3.488128641031233</v>
       </c>
       <c r="N2" t="n">
-        <v>17.76740575629621</v>
+        <v>17.66522097744541</v>
       </c>
       <c r="O2" t="n">
-        <v>4.215140063662917</v>
+        <v>4.203001424868353</v>
       </c>
       <c r="P2" t="n">
-        <v>322.9772654911348</v>
+        <v>322.9592898498788</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26797,28 +26957,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3450785885445136</v>
+        <v>-0.3474303649882512</v>
       </c>
       <c r="J3" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="K3" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4636863136462501</v>
+        <v>0.4694786005988709</v>
       </c>
       <c r="M3" t="n">
-        <v>1.930281492061516</v>
+        <v>1.928600327880243</v>
       </c>
       <c r="N3" t="n">
-        <v>6.222095178930202</v>
+        <v>6.202592141967425</v>
       </c>
       <c r="O3" t="n">
-        <v>2.494412792408306</v>
+        <v>2.490500379836836</v>
       </c>
       <c r="P3" t="n">
-        <v>323.3976464259224</v>
+        <v>323.426597221904</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26879,28 +27039,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1600829455557642</v>
+        <v>-0.1588157548327444</v>
       </c>
       <c r="J4" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="K4" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1766130638886977</v>
+        <v>0.1759480567135585</v>
       </c>
       <c r="M4" t="n">
-        <v>1.788076610283721</v>
+        <v>1.782801584459403</v>
       </c>
       <c r="N4" t="n">
-        <v>5.397309249048287</v>
+        <v>5.371651807841205</v>
       </c>
       <c r="O4" t="n">
-        <v>2.323210978161107</v>
+        <v>2.317682421696555</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1376936158095</v>
+        <v>325.1221041199337</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -26961,28 +27121,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2588930405273516</v>
+        <v>-0.2643323711618311</v>
       </c>
       <c r="J5" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="K5" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3427904694890338</v>
+        <v>0.3510849176140628</v>
       </c>
       <c r="M5" t="n">
-        <v>1.840203535778033</v>
+        <v>1.850121705338708</v>
       </c>
       <c r="N5" t="n">
-        <v>5.805262836201299</v>
+        <v>5.872553383439658</v>
       </c>
       <c r="O5" t="n">
-        <v>2.409411304904436</v>
+        <v>2.423335177692029</v>
       </c>
       <c r="P5" t="n">
-        <v>330.4406930286445</v>
+        <v>330.5076569531719</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27043,28 +27203,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2631049753342712</v>
+        <v>-0.2700791511905167</v>
       </c>
       <c r="J6" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="K6" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3117060713227371</v>
+        <v>0.3204366714238305</v>
       </c>
       <c r="M6" t="n">
-        <v>2.105241059304822</v>
+        <v>2.12023864459372</v>
       </c>
       <c r="N6" t="n">
-        <v>6.905463279213602</v>
+        <v>7.034292407724137</v>
       </c>
       <c r="O6" t="n">
-        <v>2.627824818973594</v>
+        <v>2.652224049307323</v>
       </c>
       <c r="P6" t="n">
-        <v>323.5777727066542</v>
+        <v>323.6636352036974</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27125,28 +27285,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1517097994994237</v>
+        <v>-0.157824709463482</v>
       </c>
       <c r="J7" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="K7" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07584071184155428</v>
+        <v>0.08168740442825118</v>
       </c>
       <c r="M7" t="n">
-        <v>2.864019399992311</v>
+        <v>2.874529273655895</v>
       </c>
       <c r="N7" t="n">
-        <v>12.67003230753629</v>
+        <v>12.73315470441121</v>
       </c>
       <c r="O7" t="n">
-        <v>3.559498884328564</v>
+        <v>3.568354621448268</v>
       </c>
       <c r="P7" t="n">
-        <v>326.5778329941924</v>
+        <v>326.6531385356665</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27188,7 +27348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53441,6 +53601,174 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-45.166569538449686,170.91044553306918</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-45.1669228754077,170.9096628594905</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-45.16748005333366,170.90918009360695</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-45.16794082682628,170.90853957626499</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-45.1684445308786,170.9079727980781</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-45.16898869321405,170.90753409685132</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-45.166569538449686,170.91044553306918</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-45.1669228754077,170.9096628594905</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-45.16748005333366,170.90918009360695</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-45.16794082682628,170.90853957626499</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-45.1684445308786,170.9079727980781</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-45.16897385974418,170.9075067335661</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-45.166566662427044,170.91044206679092</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-45.16691818376703,170.90965617934293</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-45.16747753751356,170.90917610655978</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-45.16793971297555,170.9085375778841</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-45.168441881609894,170.90796750050671</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-45.168975228145726,170.9075092578538</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-45.16655714416091,170.91043059506293</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-45.16692414341865,170.909664664936</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-45.16746981035093,170.90916386063134</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-45.16793536895742,170.90852978419932</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-45.168435596089076,170.90795493176094</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-45.1689664703749,170.90749310241458</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H629"/>
+  <dimension ref="A1:H635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19308,6 +19308,186 @@
         <v>316.22</v>
       </c>
       <c r="H629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="C630" t="n">
+        <v>312.73</v>
+      </c>
+      <c r="D630" t="n">
+        <v>320.52</v>
+      </c>
+      <c r="E630" t="n">
+        <v>318.82</v>
+      </c>
+      <c r="F630" t="n">
+        <v>310.36</v>
+      </c>
+      <c r="G630" t="n">
+        <v>316.06</v>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>321.24</v>
+      </c>
+      <c r="C631" t="n">
+        <v>313.09</v>
+      </c>
+      <c r="D631" t="n">
+        <v>320.58</v>
+      </c>
+      <c r="E631" t="n">
+        <v>318.74</v>
+      </c>
+      <c r="F631" t="n">
+        <v>309.12</v>
+      </c>
+      <c r="G631" t="n">
+        <v>315.97</v>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="C632" t="n">
+        <v>313.15</v>
+      </c>
+      <c r="D632" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="E632" t="n">
+        <v>319.96</v>
+      </c>
+      <c r="F632" t="n">
+        <v>309.41</v>
+      </c>
+      <c r="G632" t="n">
+        <v>316.24</v>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>320.92</v>
+      </c>
+      <c r="C633" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D633" t="n">
+        <v>318.59</v>
+      </c>
+      <c r="E633" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="F633" t="n">
+        <v>309.89</v>
+      </c>
+      <c r="G633" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="C634" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="D634" t="n">
+        <v>318.86</v>
+      </c>
+      <c r="E634" t="n">
+        <v>321.3</v>
+      </c>
+      <c r="F634" t="n">
+        <v>310.16</v>
+      </c>
+      <c r="G634" t="n">
+        <v>316.81</v>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>320.6</v>
+      </c>
+      <c r="C635" t="n">
+        <v>313.25</v>
+      </c>
+      <c r="D635" t="n">
+        <v>320</v>
+      </c>
+      <c r="E635" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="F635" t="n">
+        <v>311.12</v>
+      </c>
+      <c r="G635" t="n">
+        <v>317.65</v>
+      </c>
+      <c r="H635" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19324,7 +19504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B738"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26707,6 +26887,66 @@
       </c>
       <c r="B738" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -26875,28 +27115,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02829787087390958</v>
+        <v>-0.03042014285846486</v>
       </c>
       <c r="J2" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K2" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002057049467040772</v>
+        <v>0.002420364238879258</v>
       </c>
       <c r="M2" t="n">
-        <v>3.488128641031233</v>
+        <v>3.466033871095874</v>
       </c>
       <c r="N2" t="n">
-        <v>17.66522097744541</v>
+        <v>17.51034564080511</v>
       </c>
       <c r="O2" t="n">
-        <v>4.203001424868353</v>
+        <v>4.184536490557241</v>
       </c>
       <c r="P2" t="n">
-        <v>322.9592898498788</v>
+        <v>322.9854968410049</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26957,28 +27197,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3474303649882512</v>
+        <v>-0.3502006433515487</v>
       </c>
       <c r="J3" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K3" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4694786005988709</v>
+        <v>0.4773460269907136</v>
       </c>
       <c r="M3" t="n">
-        <v>1.928600327880243</v>
+        <v>1.923128097543263</v>
       </c>
       <c r="N3" t="n">
-        <v>6.202592141967425</v>
+        <v>6.164817093740421</v>
       </c>
       <c r="O3" t="n">
-        <v>2.490500379836836</v>
+        <v>2.482904970743025</v>
       </c>
       <c r="P3" t="n">
-        <v>323.426597221904</v>
+        <v>323.4607966663137</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27039,28 +27279,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1588157548327444</v>
+        <v>-0.1606342775416587</v>
       </c>
       <c r="J4" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K4" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1759480567135585</v>
+        <v>0.1816447066439398</v>
       </c>
       <c r="M4" t="n">
-        <v>1.782801584459403</v>
+        <v>1.776437280098408</v>
       </c>
       <c r="N4" t="n">
-        <v>5.371651807841205</v>
+        <v>5.337046307217654</v>
       </c>
       <c r="O4" t="n">
-        <v>2.317682421696555</v>
+        <v>2.310204819321796</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1221041199337</v>
+        <v>325.1445674768647</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27121,28 +27361,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2643323711618311</v>
+        <v>-0.2704790100295485</v>
       </c>
       <c r="J5" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K5" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3510849176140628</v>
+        <v>0.3618319238575201</v>
       </c>
       <c r="M5" t="n">
-        <v>1.850121705338708</v>
+        <v>1.857494110206537</v>
       </c>
       <c r="N5" t="n">
-        <v>5.872553383439658</v>
+        <v>5.923804306385301</v>
       </c>
       <c r="O5" t="n">
-        <v>2.423335177692029</v>
+        <v>2.433886666709299</v>
       </c>
       <c r="P5" t="n">
-        <v>330.5076569531719</v>
+        <v>330.5835053969618</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27203,28 +27443,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2700791511905167</v>
+        <v>-0.2827377578289856</v>
       </c>
       <c r="J6" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K6" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3204366714238305</v>
+        <v>0.3329166995967796</v>
       </c>
       <c r="M6" t="n">
-        <v>2.12023864459372</v>
+        <v>2.15197119537621</v>
       </c>
       <c r="N6" t="n">
-        <v>7.034292407724137</v>
+        <v>7.35389594249355</v>
       </c>
       <c r="O6" t="n">
-        <v>2.652224049307323</v>
+        <v>2.711806767174525</v>
       </c>
       <c r="P6" t="n">
-        <v>323.6636352036974</v>
+        <v>323.8198930667491</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27285,28 +27525,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.157824709463482</v>
+        <v>-0.1694763194922848</v>
       </c>
       <c r="J7" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K7" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08168740442825118</v>
+        <v>0.09248208550711901</v>
       </c>
       <c r="M7" t="n">
-        <v>2.874529273655895</v>
+        <v>2.90251939729923</v>
       </c>
       <c r="N7" t="n">
-        <v>12.73315470441121</v>
+        <v>12.93960481096784</v>
       </c>
       <c r="O7" t="n">
-        <v>3.568354621448268</v>
+        <v>3.597166219535572</v>
       </c>
       <c r="P7" t="n">
-        <v>326.6531385356665</v>
+        <v>326.79696178815</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27348,7 +27588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H629"/>
+  <dimension ref="A1:H635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53769,6 +54009,258 @@
         </is>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-45.16655645939352,170.91042976975888</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-45.166923763015376,170.90966412330235</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-45.16746903164455,170.9091626265457</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-45.16793548034252,170.9085299840374</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-45.16843642723242,170.9079565937437</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-45.1689655945977,170.90749148687095</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-45.166551734498384,170.91042407516164</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-45.166926045435005,170.90966737310436</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-45.1674693910475,170.9091631961237</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-45.16793503480217,170.90852918468516</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-45.16842998587103,170.90794371337861</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-45.16896510197301,170.90749057812766</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-45.16655043344025,170.91042250708432</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-45.166926425838255,170.90966791473807</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-45.167473104877786,170.9091690817632</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-45.167941829291884,170.90854137480784</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-45.168431492318575,170.90794672572179</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-45.16896657984705,170.90749330435756</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-45.166549543242574,170.91042143418935</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-45.166917232758735,170.90965482525908</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-45.16745747084827,170.9091443051246</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-45.16794578346155,170.90854846906095</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-45.16843398574883,170.90795171166948</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-45.16896696299956,170.90749401115792</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-45.16655015953327,170.9104221769628</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-45.16692255840498,170.90966240812915</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-45.16745908816191,170.90914686822452</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-45.16794929209062,170.9085547639624</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-45.168435388303244,170.90795451626525</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-45.16896969980315,170.90749905973223</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-45.1665473519867,170.91041879321725</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-45.16692705984369,170.90966881746093</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-45.167465916818884,170.90915769020356</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-45.1679555853451,170.90856605481935</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-45.16844037516288,170.90796448816243</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>-45.16897429763269,170.90750754133816</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H635"/>
+  <dimension ref="A1:H637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19488,6 +19488,66 @@
         <v>317.65</v>
       </c>
       <c r="H635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>319.6</v>
+      </c>
+      <c r="C636" t="n">
+        <v>314.02</v>
+      </c>
+      <c r="D636" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="E636" t="n">
+        <v>322.47</v>
+      </c>
+      <c r="F636" t="n">
+        <v>310.72</v>
+      </c>
+      <c r="G636" t="n">
+        <v>316.64</v>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="C637" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="D637" t="n">
+        <v>319.72</v>
+      </c>
+      <c r="E637" t="n">
+        <v>322.37</v>
+      </c>
+      <c r="F637" t="n">
+        <v>310.11</v>
+      </c>
+      <c r="G637" t="n">
+        <v>315.53</v>
+      </c>
+      <c r="H637" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19504,7 +19564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B744"/>
+  <dimension ref="A1:B747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26947,6 +27007,36 @@
       </c>
       <c r="B744" t="n">
         <v>-0.85</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -27115,28 +27205,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03042014285846486</v>
+        <v>-0.03248125203386709</v>
       </c>
       <c r="J2" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K2" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002420364238879258</v>
+        <v>0.002770981792847294</v>
       </c>
       <c r="M2" t="n">
-        <v>3.466033871095874</v>
+        <v>3.465598348002906</v>
       </c>
       <c r="N2" t="n">
-        <v>17.51034564080511</v>
+        <v>17.48707929626762</v>
       </c>
       <c r="O2" t="n">
-        <v>4.184536490557241</v>
+        <v>4.181755528036954</v>
       </c>
       <c r="P2" t="n">
-        <v>322.9854968410049</v>
+        <v>323.0110525880287</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27197,28 +27287,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3502006433515487</v>
+        <v>-0.3504730147368013</v>
       </c>
       <c r="J3" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K3" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4773460269907136</v>
+        <v>0.4792779890733821</v>
       </c>
       <c r="M3" t="n">
-        <v>1.923128097543263</v>
+        <v>1.918338029107429</v>
       </c>
       <c r="N3" t="n">
-        <v>6.164817093740421</v>
+        <v>6.146362087986691</v>
       </c>
       <c r="O3" t="n">
-        <v>2.482904970743025</v>
+        <v>2.479185771173006</v>
       </c>
       <c r="P3" t="n">
-        <v>323.4607966663137</v>
+        <v>323.4641748041134</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27279,28 +27369,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1606342775416587</v>
+        <v>-0.1613507870335049</v>
       </c>
       <c r="J4" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K4" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1816447066439398</v>
+        <v>0.1838162809127442</v>
       </c>
       <c r="M4" t="n">
-        <v>1.776437280098408</v>
+        <v>1.774564650641058</v>
       </c>
       <c r="N4" t="n">
-        <v>5.337046307217654</v>
+        <v>5.323982877873939</v>
       </c>
       <c r="O4" t="n">
-        <v>2.310204819321796</v>
+        <v>2.307375755674385</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1445674768647</v>
+        <v>325.1534508624437</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27361,28 +27451,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2704790100295485</v>
+        <v>-0.2710815516101833</v>
       </c>
       <c r="J5" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K5" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3618319238575201</v>
+        <v>0.3642236500713004</v>
       </c>
       <c r="M5" t="n">
-        <v>1.857494110206537</v>
+        <v>1.854114895500312</v>
       </c>
       <c r="N5" t="n">
-        <v>5.923804306385301</v>
+        <v>5.907812090343333</v>
       </c>
       <c r="O5" t="n">
-        <v>2.433886666709299</v>
+        <v>2.43059912168653</v>
       </c>
       <c r="P5" t="n">
-        <v>330.5835053969618</v>
+        <v>330.5909758909061</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27443,28 +27533,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2827377578289856</v>
+        <v>-0.2865595268807867</v>
       </c>
       <c r="J6" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K6" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3329166995967796</v>
+        <v>0.3371113254626501</v>
       </c>
       <c r="M6" t="n">
-        <v>2.15197119537621</v>
+        <v>2.161259848867253</v>
       </c>
       <c r="N6" t="n">
-        <v>7.35389594249355</v>
+        <v>7.436823601369188</v>
       </c>
       <c r="O6" t="n">
-        <v>2.711806767174525</v>
+        <v>2.72705401511763</v>
       </c>
       <c r="P6" t="n">
-        <v>323.8198930667491</v>
+        <v>323.8672765261416</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27525,28 +27615,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1694763194922848</v>
+        <v>-0.1735244085401743</v>
       </c>
       <c r="J7" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K7" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09248208550711901</v>
+        <v>0.09626942483726331</v>
       </c>
       <c r="M7" t="n">
-        <v>2.90251939729923</v>
+        <v>2.912460659000784</v>
       </c>
       <c r="N7" t="n">
-        <v>12.93960481096784</v>
+        <v>13.01853950968</v>
       </c>
       <c r="O7" t="n">
-        <v>3.597166219535572</v>
+        <v>3.608121326906844</v>
       </c>
       <c r="P7" t="n">
-        <v>326.79696178815</v>
+        <v>326.8471520826901</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27588,7 +27678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H635"/>
+  <dimension ref="A1:H637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54261,6 +54351,90 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-45.16654050431173,170.9104105401807</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-45.166931941685284,170.90967576842746</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-45.16746453910747,170.9091555068216</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-45.16795580811514,170.9085664544957</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-45.1684382973048,170.90796033320507</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-45.16896876928996,170.90749734321693</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-45.166532629484834,170.9104010491911</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-45.1669273768464,170.90966926882234</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-45.16746423960498,170.90915503217337</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-45.167955251190016,170.90856545530474</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-45.16843512857096,170.90795399689566</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-45.168962693585556,170.90748613538298</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
